--- a/stories/arbres/TREE-TMP-006.xlsx
+++ b/stories/arbres/TREE-TMP-006.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Zoé est sous le pommier, avec papa. L'air pique un peu. Papa dit : s'il fait froid, on prend le manteau. S'il pleut, on prend les bottes. Zoé touche le manteau. Froid, manteau. Une goutte tombe. Pluie, bottes. Zoé pose le pied près des bottes. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
+          <t>Zoé est sous le pommier, avec papa. L'air pique un peu. S'il fait froid, on prend le manteau. S'il pleut, on prend les bottes. Zoé touche le manteau. Froid, manteau. Une goutte tombe. Pluie, bottes. Zoé pose le pied près des bottes. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé est sous le pommier, avec papa. L'air pique un peu.
+papa|S'il fait froid, on prend le manteau. S'il pleut, on prend les bottes.
+narrateur|Zoé touche le manteau. Froid, manteau. Une goutte tombe. Pluie, bottes. Zoé pose le pied près des bottes. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1493,6 +1517,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -1657,6 +1686,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé choisit rouge, comme le manteau. Froid, manteau. Papa montre aussi les bottes. Pluie, bottes. Zoé écoute. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1871,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Il fait froid. On prend quoi ?</t>
         </is>
       </c>
     </row>
@@ -2005,6 +2044,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a pris le manteau. Froid, manteau. Papa montre les bottes. Pluie, bottes. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2195,6 +2239,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2357,6 +2406,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé prend le ballon rouge. Ça sent le pain tiède. Zoé pose le ballon rouge. Le vent est froid. Froid, manteau. Pluie, bottes. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2547,6 +2601,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2709,6 +2768,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé s'approche de le chat. La lumière est claire. On caresse le tissu. Froid, manteau. Pluie, bottes. Le pommier tremble un peu. S'il fait froid, le manteau. S'il pleut, les bottes. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2871,6 +2935,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3033,6 +3102,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé s'approche de le chien. Des miettes dorment sur la table. On tend la main. Froid, manteau. Pluie, bottes. Une goutte encore. S'il fait froid, le manteau. S'il pleut, les bottes. Papa serre Zoé tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3195,6 +3269,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3357,6 +3436,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé s'approche de la poule. Un chat miaule une fois. On chante un petit air. Froid, manteau. Pluie, bottes. Le manteau est chaud. S'il fait froid, le manteau. S'il pleut, les bottes. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3519,6 +3603,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3681,6 +3770,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé prend le seau bleu. La laine gratte un peu. Le seau bleu peut servir.. Non. Les bottes, s'il pleut. Froid, manteau. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3871,6 +3965,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3895,7 +3994,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Zoé s'approche de le chat. Les chaussures font toc toc. On compte jusqu'à trois. Froid, manteau. Pluie, bottes. Les bottes sont prêtes. S'il fait froid, le manteau. S'il pleut, les bottes. Zoé range. Papa dit : c'est bien.</t>
+          <t>Zoé s'approche de le chat. Les chaussures font toc toc. On compte jusqu'à trois. Froid, manteau. Pluie, bottes. Les bottes sont prêtes. S'il fait froid, le manteau. S'il pleut, les bottes. Zoé range. C'est bien.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4033,6 +4132,12 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé s'approche de le chat. Les chaussures font toc toc. On compte jusqu'à trois. Froid, manteau. Pluie, bottes. Les bottes sont prêtes. S'il fait froid, le manteau. S'il pleut, les bottes. Zoé range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4195,6 +4300,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4357,6 +4467,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé s'approche de le chien. La couverture est douce. On montre du doigt. Froid, manteau. Pluie, bottes. Le pommier tremble un peu. S'il fait froid, le manteau. S'il pleut, les bottes. On souffle. Zoé sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4519,6 +4634,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4681,6 +4801,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé s'approche de la poule. Une cloche tinte au loin. On range la chaise. Froid, manteau. Pluie, bottes. Une goutte encore. S'il fait froid, le manteau. S'il pleut, les bottes. Zoé prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4843,6 +4968,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5005,6 +5135,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé prend le doudou. La terre est un peu humide. Le doudou chauffe. Froid, manteau. Une goutte. Pluie, bottes. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5195,6 +5330,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5357,6 +5497,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé s'approche de le chat. Le bois sent le chaud. On range un objet. Froid, manteau. Pluie, bottes. Le manteau est chaud. S'il fait froid, le manteau. S'il pleut, les bottes. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5519,6 +5664,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5681,6 +5831,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé s'approche de le chien. Une goutte tombe, ploc. On se tient la main. Froid, manteau. Pluie, bottes. Les bottes sont prêtes. S'il fait froid, le manteau. S'il pleut, les bottes. Papa serre Zoé tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5843,6 +5998,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6005,6 +6165,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé s'approche de la poule. Le savon sent la fleur. On dit merci. Froid, manteau. Pluie, bottes. Le pommier tremble un peu. S'il fait froid, le manteau. S'il pleut, les bottes. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6167,6 +6332,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6191,7 +6361,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Zoé choisit bleu, comme le ciel. Une goutte. Pluie, bottes. Papa dit : et s'il fait froid, manteau. Froid, manteau. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
+          <t>Zoé choisit bleu, comme le ciel. Une goutte. Pluie, bottes. Et s'il fait froid, manteau. Froid, manteau. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6329,6 +6499,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé choisit bleu, comme le ciel. Une goutte. Pluie, bottes.
+papa|Et s'il fait froid, manteau. Froid, manteau. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6505,6 +6681,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Il pleut. On prend quoi ?</t>
         </is>
       </c>
     </row>
@@ -6673,6 +6854,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Pluie, bottes. Froid, manteau. Zoé a retenu. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6863,6 +7049,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6887,7 +7078,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Zoé prend le ballon rouge. La laine gratte un peu. Le ballon est froid. Papa dit : manteau. Froid, manteau. Pluie, bottes. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
+          <t>Zoé prend le ballon rouge. La laine gratte un peu. Le ballon est froid. Manteau. Froid, manteau. Pluie, bottes. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7025,6 +7216,12 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé prend le ballon rouge. La laine gratte un peu. Le ballon est froid.
+papa|Manteau. Froid, manteau. Pluie, bottes. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7215,6 +7412,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7239,7 +7441,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Zoé s'approche de le chat. Le tissu est tout doux. On souffle doucement. Froid, manteau. Pluie, bottes. Une goutte encore. S'il fait froid, le manteau. S'il pleut, les bottes. Zoé range. Papa dit : c'est bien.</t>
+          <t>Zoé s'approche de le chat. Le tissu est tout doux. On souffle doucement. Froid, manteau. Pluie, bottes. Une goutte encore. S'il fait froid, le manteau. S'il pleut, les bottes. Zoé range. C'est bien.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7377,6 +7579,12 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé s'approche de le chat. Le tissu est tout doux. On souffle doucement. Froid, manteau. Pluie, bottes. Une goutte encore. S'il fait froid, le manteau. S'il pleut, les bottes. Zoé range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7539,6 +7747,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7701,6 +7914,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé s'approche de le chien. Une cuillère tinte. On écoute jusqu'au bout. Froid, manteau. Pluie, bottes. Le manteau est chaud. S'il fait froid, le manteau. S'il pleut, les bottes. On souffle. Zoé sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7863,6 +8081,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8025,6 +8248,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé s'approche de la poule. Le sable est tiède. On attend son tour. Froid, manteau. Pluie, bottes. Les bottes sont prêtes. S'il fait froid, le manteau. S'il pleut, les bottes. Zoé prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8187,6 +8415,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8349,6 +8582,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé prend le seau bleu. Une cuillère tinte. Zoé range le seau. Les bottes attendent. Pluie, bottes. Froid, manteau. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8539,6 +8777,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8701,6 +8944,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé s'approche de le chat. Un rire court, tout petit. On sourit ensemble. Froid, manteau. Pluie, bottes. Le pommier tremble un peu. S'il fait froid, le manteau. S'il pleut, les bottes. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8863,6 +9111,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9025,6 +9278,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé s'approche de le chien. Le papier froisse, chut. On pose les pieds par terre. Froid, manteau. Pluie, bottes. Une goutte encore. S'il fait froid, le manteau. S'il pleut, les bottes. Papa serre Zoé tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9187,6 +9445,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9349,6 +9612,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé s'approche de la poule. L'herbe chatouille le mollet. On parle tout bas. Froid, manteau. Pluie, bottes. Le manteau est chaud. S'il fait froid, le manteau. S'il pleut, les bottes. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9511,6 +9779,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9673,6 +9946,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé prend le doudou. Le sable est tiède. Zoé serre le doudou. Papa boutonne le manteau. Froid, manteau. Pluie, bottes. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9863,6 +10141,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9887,7 +10170,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Zoé s'approche de le chat. Un pigeon roucoule. On range les jouets. Froid, manteau. Pluie, bottes. Les bottes sont prêtes. S'il fait froid, le manteau. S'il pleut, les bottes. Zoé range. Papa dit : c'est bien.</t>
+          <t>Zoé s'approche de le chat. Un pigeon roucoule. On range les jouets. Froid, manteau. Pluie, bottes. Les bottes sont prêtes. S'il fait froid, le manteau. S'il pleut, les bottes. Zoé range. C'est bien.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10025,6 +10308,12 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé s'approche de le chat. Un pigeon roucoule. On range les jouets. Froid, manteau. Pluie, bottes. Les bottes sont prêtes. S'il fait froid, le manteau. S'il pleut, les bottes. Zoé range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10187,6 +10476,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10349,6 +10643,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé s'approche de le chien. La fenêtre vibre un peu. On s'assoit un moment. Froid, manteau. Pluie, bottes. Le pommier tremble un peu. S'il fait froid, le manteau. S'il pleut, les bottes. On souffle. Zoé sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10511,6 +10810,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10673,6 +10977,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé s'approche de la poule. Le lait est froid dans le verre. On respire, un, deux. Froid, manteau. Pluie, bottes. Une goutte encore. S'il fait froid, le manteau. S'il pleut, les bottes. Zoé prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10835,6 +11144,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10997,6 +11311,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé choisit vert, comme l'herbe mouillée. Pluie, bottes. Le vent est froid. Froid, manteau. Zoé s'approche de papa. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11173,6 +11492,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Manteau ou bottes. Selon quoi ?</t>
         </is>
       </c>
     </row>
@@ -11341,6 +11665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Papa confirme. Manteau s'il fait froid. Bottes s'il pleut. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11531,6 +11860,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11693,6 +12027,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé prend le ballon rouge. Le savon mousse entre les doigts. Le ballon reste. Zoé enfile le manteau. Froid, manteau. Pluie, bottes. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11883,6 +12222,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12045,6 +12389,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé s'approche de le chat. La corde du sac est rêche. On referme le sac. Froid, manteau. Pluie, bottes. Le manteau est chaud. S'il fait froid, le manteau. S'il pleut, les bottes. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12207,6 +12556,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12369,6 +12723,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé s'approche de le chien. Le savon mousse entre les doigts. On essuie une miette. Froid, manteau. Pluie, bottes. Les bottes sont prêtes. S'il fait froid, le manteau. S'il pleut, les bottes. Papa serre Zoé tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12531,6 +12890,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12693,6 +13057,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé s'approche de la poule. Un ruisseau chante. On met le doudou près. Froid, manteau. Pluie, bottes. Le pommier tremble un peu. S'il fait froid, le manteau. S'il pleut, les bottes. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12855,6 +13224,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13017,6 +13391,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé prend le seau bleu. Un ruisseau chante. Le seau fait ploc. Pluie, bottes. Froid, manteau. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13207,6 +13586,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13231,7 +13615,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Zoé s'approche de le chat. La laine gratte un peu. On lace les chaussures. Froid, manteau. Pluie, bottes. Une goutte encore. S'il fait froid, le manteau. S'il pleut, les bottes. Zoé range. Papa dit : c'est bien.</t>
+          <t>Zoé s'approche de le chat. La laine gratte un peu. On lace les chaussures. Froid, manteau. Pluie, bottes. Une goutte encore. S'il fait froid, le manteau. S'il pleut, les bottes. Zoé range. C'est bien.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13369,6 +13753,12 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé s'approche de le chat. La laine gratte un peu. On lace les chaussures. Froid, manteau. Pluie, bottes. Une goutte encore. S'il fait froid, le manteau. S'il pleut, les bottes. Zoé range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13531,6 +13921,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13693,6 +14088,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé s'approche de le chien. Un pain croustille. On met le manteau. Froid, manteau. Pluie, bottes. Le manteau est chaud. S'il fait froid, le manteau. S'il pleut, les bottes. On souffle. Zoé sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13855,6 +14255,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14017,6 +14422,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé s'approche de la poule. Le savon glisse. On boit une gorgée. Froid, manteau. Pluie, bottes. Les bottes sont prêtes. S'il fait froid, le manteau. S'il pleut, les bottes. Zoé prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14179,6 +14589,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14341,6 +14756,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé prend le doudou. Le papier froisse, chut. Le doudou rentre dans le sac. Manteau. Bottes. Froid. Pluie. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14531,6 +14951,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14693,6 +15118,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé s'approche de le chat. Une plume vole. On feuillette le livre. Froid, manteau. Pluie, bottes. Le pommier tremble un peu. S'il fait froid, le manteau. S'il pleut, les bottes. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14855,6 +15285,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15017,6 +15452,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé s'approche de le chien. Le banc est lisse. On referme le livre. Froid, manteau. Pluie, bottes. Une goutte encore. S'il fait froid, le manteau. S'il pleut, les bottes. Papa serre Zoé tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15179,6 +15619,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15341,6 +15786,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé s'approche de la poule. Un grelot sonne. On pose le ballon. Froid, manteau. Pluie, bottes. Le manteau est chaud. S'il fait froid, le manteau. S'il pleut, les bottes. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15503,6 +15953,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15521,7 +15976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15538,6 +15993,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>ch1: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-TMP-006.xlsx
+++ b/stories/arbres/TREE-TMP-006.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Zoé touche le manteau. Froid, manteau. Une goutte tombe. Pluie, bottes. Zoé pose le pied près des bottes. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1524,6 +1530,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1691,6 +1698,7 @@
           <t>narrateur|Zoé choisit rouge, comme le manteau. Froid, manteau. Papa montre aussi les bottes. Pluie, bottes. Zoé écoute. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1878,6 +1886,7 @@
           <t>narrateur|Il fait froid. On prend quoi ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2049,6 +2058,7 @@
           <t>narrateur|Zoé a pris le manteau. Froid, manteau. Papa montre les bottes. Pluie, bottes. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2244,6 +2254,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2411,6 +2422,7 @@
           <t>narrateur|Zoé prend le ballon rouge. Ça sent le pain tiède. Zoé pose le ballon rouge. Le vent est froid. Froid, manteau. Pluie, bottes. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2604,6 +2616,11 @@
       <c r="AW9" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -2773,6 +2790,7 @@
           <t>narrateur|Zoé s'approche de le chat. La lumière est claire. On caresse le tissu. Froid, manteau. Pluie, bottes. Le pommier tremble un peu. S'il fait froid, le manteau. S'il pleut, les bottes. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2940,6 +2958,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3107,6 +3126,11 @@
           <t>narrateur|Zoé s'approche de le chien. Des miettes dorment sur la table. On tend la main. Froid, manteau. Pluie, bottes. Une goutte encore. S'il fait froid, le manteau. S'il pleut, les bottes. Papa serre Zoé tout doux.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3274,6 +3298,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3441,6 +3466,7 @@
           <t>narrateur|Zoé s'approche de la poule. Un chat miaule une fois. On chante un petit air. Froid, manteau. Pluie, bottes. Le manteau est chaud. S'il fait froid, le manteau. S'il pleut, les bottes. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3608,6 +3634,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3775,6 +3802,7 @@
           <t>narrateur|Zoé prend le seau bleu. La laine gratte un peu. Le seau bleu peut servir.. Non. Les bottes, s'il pleut. Froid, manteau. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3968,6 +3996,11 @@
       <c r="AW17" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -4138,6 +4171,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4305,6 +4339,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4472,6 +4507,11 @@
           <t>narrateur|Zoé s'approche de le chien. La couverture est douce. On montre du doigt. Froid, manteau. Pluie, bottes. Le pommier tremble un peu. S'il fait froid, le manteau. S'il pleut, les bottes. On souffle. Zoé sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4639,6 +4679,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4806,6 +4847,7 @@
           <t>narrateur|Zoé s'approche de la poule. Une cloche tinte au loin. On range la chaise. Froid, manteau. Pluie, bottes. Une goutte encore. S'il fait froid, le manteau. S'il pleut, les bottes. Zoé prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4973,6 +5015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5140,6 +5183,7 @@
           <t>narrateur|Zoé prend le doudou. La terre est un peu humide. Le doudou chauffe. Froid, manteau. Une goutte. Pluie, bottes. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5333,6 +5377,11 @@
       <c r="AW25" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -5502,6 +5551,7 @@
           <t>narrateur|Zoé s'approche de le chat. Le bois sent le chaud. On range un objet. Froid, manteau. Pluie, bottes. Le manteau est chaud. S'il fait froid, le manteau. S'il pleut, les bottes. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5669,6 +5719,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5836,6 +5887,11 @@
           <t>narrateur|Zoé s'approche de le chien. Une goutte tombe, ploc. On se tient la main. Froid, manteau. Pluie, bottes. Les bottes sont prêtes. S'il fait froid, le manteau. S'il pleut, les bottes. Papa serre Zoé tout doux.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6003,6 +6059,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6170,6 +6227,7 @@
           <t>narrateur|Zoé s'approche de la poule. Le savon sent la fleur. On dit merci. Froid, manteau. Pluie, bottes. Le pommier tremble un peu. S'il fait froid, le manteau. S'il pleut, les bottes. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6337,6 +6395,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6505,6 +6564,7 @@
 papa|Et s'il fait froid, manteau. Froid, manteau. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6688,6 +6748,7 @@
           <t>narrateur|Il pleut. On prend quoi ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6859,6 +6920,7 @@
           <t>narrateur|Pluie, bottes. Froid, manteau. Zoé a retenu. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7054,6 +7116,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7222,6 +7285,7 @@
 papa|Manteau. Froid, manteau. Pluie, bottes. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7415,6 +7479,11 @@
       <c r="AW37" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -7585,6 +7654,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7752,6 +7822,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7919,6 +7990,11 @@
           <t>narrateur|Zoé s'approche de le chien. Une cuillère tinte. On écoute jusqu'au bout. Froid, manteau. Pluie, bottes. Le manteau est chaud. S'il fait froid, le manteau. S'il pleut, les bottes. On souffle. Zoé sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8086,6 +8162,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8253,6 +8330,7 @@
           <t>narrateur|Zoé s'approche de la poule. Le sable est tiède. On attend son tour. Froid, manteau. Pluie, bottes. Les bottes sont prêtes. S'il fait froid, le manteau. S'il pleut, les bottes. Zoé prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8420,6 +8498,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8587,6 +8666,7 @@
           <t>narrateur|Zoé prend le seau bleu. Une cuillère tinte. Zoé range le seau. Les bottes attendent. Pluie, bottes. Froid, manteau. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8780,6 +8860,11 @@
       <c r="AW45" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -8949,6 +9034,7 @@
           <t>narrateur|Zoé s'approche de le chat. Un rire court, tout petit. On sourit ensemble. Froid, manteau. Pluie, bottes. Le pommier tremble un peu. S'il fait froid, le manteau. S'il pleut, les bottes. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9116,6 +9202,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9283,6 +9370,11 @@
           <t>narrateur|Zoé s'approche de le chien. Le papier froisse, chut. On pose les pieds par terre. Froid, manteau. Pluie, bottes. Une goutte encore. S'il fait froid, le manteau. S'il pleut, les bottes. Papa serre Zoé tout doux.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9450,6 +9542,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9617,6 +9710,7 @@
           <t>narrateur|Zoé s'approche de la poule. L'herbe chatouille le mollet. On parle tout bas. Froid, manteau. Pluie, bottes. Le manteau est chaud. S'il fait froid, le manteau. S'il pleut, les bottes. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9784,6 +9878,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9951,6 +10046,7 @@
           <t>narrateur|Zoé prend le doudou. Le sable est tiède. Zoé serre le doudou. Papa boutonne le manteau. Froid, manteau. Pluie, bottes. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10144,6 +10240,11 @@
       <c r="AW53" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -10314,6 +10415,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10481,6 +10583,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10648,6 +10751,11 @@
           <t>narrateur|Zoé s'approche de le chien. La fenêtre vibre un peu. On s'assoit un moment. Froid, manteau. Pluie, bottes. Le pommier tremble un peu. S'il fait froid, le manteau. S'il pleut, les bottes. On souffle. Zoé sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10815,6 +10923,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10982,6 +11091,7 @@
           <t>narrateur|Zoé s'approche de la poule. Le lait est froid dans le verre. On respire, un, deux. Froid, manteau. Pluie, bottes. Une goutte encore. S'il fait froid, le manteau. S'il pleut, les bottes. Zoé prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11149,6 +11259,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11316,6 +11427,7 @@
           <t>narrateur|Zoé choisit vert, comme l'herbe mouillée. Pluie, bottes. Le vent est froid. Froid, manteau. Zoé s'approche de papa. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11499,6 +11611,7 @@
           <t>narrateur|Manteau ou bottes. Selon quoi ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11670,6 +11783,7 @@
           <t>narrateur|Papa confirme. Manteau s'il fait froid. Bottes s'il pleut. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11865,6 +11979,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12032,6 +12147,7 @@
           <t>narrateur|Zoé prend le ballon rouge. Le savon mousse entre les doigts. Le ballon reste. Zoé enfile le manteau. Froid, manteau. Pluie, bottes. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12225,6 +12341,11 @@
       <c r="AW65" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -12394,6 +12515,7 @@
           <t>narrateur|Zoé s'approche de le chat. La corde du sac est rêche. On referme le sac. Froid, manteau. Pluie, bottes. Le manteau est chaud. S'il fait froid, le manteau. S'il pleut, les bottes. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12561,6 +12683,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12728,6 +12851,11 @@
           <t>narrateur|Zoé s'approche de le chien. Le savon mousse entre les doigts. On essuie une miette. Froid, manteau. Pluie, bottes. Les bottes sont prêtes. S'il fait froid, le manteau. S'il pleut, les bottes. Papa serre Zoé tout doux.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12895,6 +13023,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13062,6 +13191,7 @@
           <t>narrateur|Zoé s'approche de la poule. Un ruisseau chante. On met le doudou près. Froid, manteau. Pluie, bottes. Le pommier tremble un peu. S'il fait froid, le manteau. S'il pleut, les bottes. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13229,6 +13359,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13396,6 +13527,7 @@
           <t>narrateur|Zoé prend le seau bleu. Un ruisseau chante. Le seau fait ploc. Pluie, bottes. Froid, manteau. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13589,6 +13721,11 @@
       <c r="AW73" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -13759,6 +13896,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13926,6 +14064,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14093,6 +14232,11 @@
           <t>narrateur|Zoé s'approche de le chien. Un pain croustille. On met le manteau. Froid, manteau. Pluie, bottes. Le manteau est chaud. S'il fait froid, le manteau. S'il pleut, les bottes. On souffle. Zoé sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14260,6 +14404,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14427,6 +14572,7 @@
           <t>narrateur|Zoé s'approche de la poule. Le savon glisse. On boit une gorgée. Froid, manteau. Pluie, bottes. Les bottes sont prêtes. S'il fait froid, le manteau. S'il pleut, les bottes. Zoé prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14594,6 +14740,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14761,6 +14908,7 @@
           <t>narrateur|Zoé prend le doudou. Le papier froisse, chut. Le doudou rentre dans le sac. Manteau. Bottes. Froid. Pluie. S'il fait froid, le manteau. S'il pleut, les bottes.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14954,6 +15102,11 @@
       <c r="AW81" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -15123,6 +15276,7 @@
           <t>narrateur|Zoé s'approche de le chat. Une plume vole. On feuillette le livre. Froid, manteau. Pluie, bottes. Le pommier tremble un peu. S'il fait froid, le manteau. S'il pleut, les bottes. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15290,6 +15444,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15457,6 +15612,11 @@
           <t>narrateur|Zoé s'approche de le chien. Le banc est lisse. On referme le livre. Froid, manteau. Pluie, bottes. Une goutte encore. S'il fait froid, le manteau. S'il pleut, les bottes. Papa serre Zoé tout doux.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15624,6 +15784,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15791,6 +15952,7 @@
           <t>narrateur|Zoé s'approche de la poule. Un grelot sonne. On pose le ballon. Froid, manteau. Pluie, bottes. Le manteau est chaud. S'il fait froid, le manteau. S'il pleut, les bottes. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15958,6 +16120,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15976,7 +16139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16000,6 +16163,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16014,7 +16191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16201,6 +16378,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
